--- a/reports/Japan_Strikers_Scouting.xlsx
+++ b/reports/Japan_Strikers_Scouting.xlsx
@@ -8,13 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="Strikers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Uncertainty" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Archetype Z" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Shortlist" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Uncertainty" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Archetype Z" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Strikers'!$A$1:$O$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Uncertainty'!$A$1:$H$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shortlist'!$A$1:$J$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Uncertainty'!$A$1:$H$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,7 +38,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +48,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001D4ED8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,11 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4742,6 +4750,1873 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Primary Archetype</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Minutes</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Scouting Score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Uncertainty Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Target Striker</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>R. Arita</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kagoshima United</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2" t="n">
+        <v>885</v>
+      </c>
+      <c r="G2" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Very Good Target Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Target Striker</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>D. Furukawa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Renofa Yamaguchi</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1177</v>
+      </c>
+      <c r="G3" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>High confidence</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Solid Target Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Target Striker</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>T. Nakashima</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Thespa Gunma</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>High confidence</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Solid Target Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Target Striker</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Patric</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Zweigen Kanazawa</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F5" t="n">
+        <v>733</v>
+      </c>
+      <c r="G5" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Low confidence</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Solid Target Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Target Striker</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>K. Sagawa</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Blaublitz Akita</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1020</v>
+      </c>
+      <c r="G6" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Solid Target Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Target Striker</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Matheus Peixoto</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Júbilo Iwata</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1104</v>
+      </c>
+      <c r="G7" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Solid Target Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Target Striker</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>K. Buwanika</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Zweigen Kanazawa</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>23</v>
+      </c>
+      <c r="F8" t="n">
+        <v>918</v>
+      </c>
+      <c r="G8" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Solid Target Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Target Striker</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R. Ota</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ventforet Kofu</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>967</v>
+      </c>
+      <c r="G9" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Solid Target Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Target Striker</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>T. Kato</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Matsumoto Yamaga</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>26</v>
+      </c>
+      <c r="F10" t="n">
+        <v>952</v>
+      </c>
+      <c r="G10" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>26</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Solid Target Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Target Striker</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>K. Watanabe</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Shonan Bellmare</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>23</v>
+      </c>
+      <c r="F11" t="n">
+        <v>883</v>
+      </c>
+      <c r="G11" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Fringe Target Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Goalscoring Striker</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Lucas Barcelos</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Tokushima Vortis</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>1192</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>High confidence</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Very Good Goalscoring Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Goalscoring Striker</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>K. Tsuboi</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Kataller Toyama</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>766</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Very Good Goalscoring Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Goalscoring Striker</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>H. Iwabuchi</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Vegalta Sendai</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1068</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>High confidence</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Very Good Goalscoring Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Goalscoring Striker</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Y. Taguchi</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Ehime</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>954</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Very Good Goalscoring Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Goalscoring Striker</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>S. Tamura</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Nara Club</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>1409</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>High confidence</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Solid Goalscoring Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Goalscoring Striker</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Y. Toshida</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Tegevajaro Miyazaki</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>1286</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>High confidence</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Solid Goalscoring Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Goalscoring Striker</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>A. Bakayoko</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Consadole Sapporo</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>722</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Solid Goalscoring Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Goalscoring Striker</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>M. Shintani</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Kochi United</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>1225</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>High confidence</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Solid Goalscoring Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Goalscoring Striker</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>S. Omori</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Consadole Sapporo</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>735</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Solid Goalscoring Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Goalscoring Striker</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>H. Yamada</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Shonan Bellmare</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1195</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>High confidence</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Solid Goalscoring Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Second Striker</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Thonny Anderson</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Tokushima Vortis</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>28</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1280</v>
+      </c>
+      <c r="G22" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Very Good Second Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Second Striker</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Edigar Junio</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Imabari</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>35</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1138</v>
+      </c>
+      <c r="G23" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>High confidence</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Solid Second Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Second Striker</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>K. Murakoshi</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Matsumoto Yamaga</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1564</v>
+      </c>
+      <c r="G24" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>High confidence</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Solid Second Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Second Striker</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Y. Nishimura</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Thespa Gunma</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>26</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1378</v>
+      </c>
+      <c r="G25" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Fringe Second Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Second Striker</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>H. Asakawa</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ryūkyū</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>31</v>
+      </c>
+      <c r="F26" t="n">
+        <v>892</v>
+      </c>
+      <c r="G26" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Fringe Second Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Second Striker</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>T. Kitsui</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Osaka</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>33</v>
+      </c>
+      <c r="F27" t="n">
+        <v>996</v>
+      </c>
+      <c r="G27" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Fringe Second Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Second Striker</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>K. Kawamura</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kagoshima United</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1348</v>
+      </c>
+      <c r="G28" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>High confidence</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Fringe Second Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Second Striker</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>R. Watanabe</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Júbilo Iwata</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>29</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1054</v>
+      </c>
+      <c r="G29" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Fringe Second Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Second Striker</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>A. Inoue</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Matsumoto Yamaga</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" t="n">
+        <v>721</v>
+      </c>
+      <c r="G30" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Fringe Second Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Second Striker</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>K. Fujikawa</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Parceiro Nagano</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>27</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1208</v>
+      </c>
+      <c r="G31" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Fringe Second Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Striker</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Matheus Moraes</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>917</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Very Good Dynamic Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Striker</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>R. Kawamoto</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Gifu</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>1558</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>High confidence</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Very Good Dynamic Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Striker</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>R. Shiohama</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Sagan Tosu</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Very Good Dynamic Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Striker</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Gustavo Silva</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Júbilo Iwata</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>1086</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Solid Dynamic Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Striker</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>K. Mori</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Imabari</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>916</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Solid Dynamic Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Striker</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Y. Wakatsuki</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1096</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Solid Dynamic Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Striker</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>T. Kato</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Iwaki</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Fringe Dynamic Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Striker</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>K. Kasai</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>1123</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>High confidence</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Fringe Dynamic Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Striker</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>M. Handai</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Roasso Kumamoto</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>722</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Fringe Dynamic Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Striker</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>K. Hoshi</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Gainare Tottori</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>945</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Fringe Dynamic Striker</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Complete Forward</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>T. Nishino</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Tochigi SC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>23</v>
+      </c>
+      <c r="F42" t="n">
+        <v>800</v>
+      </c>
+      <c r="G42" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Elite Complete Forward</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Complete Forward</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>K. Shimizu</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Fukushima United</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" t="n">
+        <v>852</v>
+      </c>
+      <c r="G43" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Medium confidence</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Elite Complete Forward</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J43"/>
+  <conditionalFormatting sqref="G2:G43">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F87171"/>
+        <color rgb="00FEF08A"/>
+        <color rgb="004ADE80"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H43">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="004ADE80"/>
+        <color rgb="00FEF08A"/>
+        <color rgb="00F87171"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6975,7 +8850,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13001,7 +14876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/reports/Japan_Strikers_Scouting.xlsx
+++ b/reports/Japan_Strikers_Scouting.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Strikers'!$A$1:$O$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shortlist'!$A$1:$J$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Shortlist'!$A$1:$J$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Uncertainty'!$A$1:$H$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4750,7 +4750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6497,93 +6497,9 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Complete Forward</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>T. Nishino</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Tochigi SC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>23</v>
-      </c>
-      <c r="F42" t="n">
-        <v>800</v>
-      </c>
-      <c r="G42" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="H42" t="n">
-        <v>30</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Medium confidence</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Elite Complete Forward</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Complete Forward</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>2</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>K. Shimizu</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Fukushima United</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>24</v>
-      </c>
-      <c r="F43" t="n">
-        <v>852</v>
-      </c>
-      <c r="G43" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="H43" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Medium confidence</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Elite Complete Forward</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J43"/>
-  <conditionalFormatting sqref="G2:G43">
+  <autoFilter ref="A1:J41"/>
+  <conditionalFormatting sqref="G2:G41">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6595,7 +6511,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H43">
+  <conditionalFormatting sqref="H2:H41">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
